--- a/dashboard_xbox.xlsx
+++ b/dashboard_xbox.xlsx
@@ -1,25 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\www\planilhas\dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnZos\Desktop\projetoDIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2F8ED6-40B2-4E08-832A-7140AC03FA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8FB1A8-6F9B-4157-94A3-2FA3B9F355AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{28DD5B76-0634-4F87-BE60-8BFA7EF2E23B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="0" firstSheet="3" activeTab="3" xr2:uid="{28DD5B76-0634-4F87-BE60-8BFA7EF2E23B}"/>
   </bookViews>
   <sheets>
-    <sheet name="A̳ssets" sheetId="1" r:id="rId1"/>
-    <sheet name="B̳ases" sheetId="2" r:id="rId2"/>
-    <sheet name="C̳álculos" sheetId="3" r:id="rId3"/>
+    <sheet name="A̳ssets" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="B̳ases" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="C̳álculos" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="D̳ashboard" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="SegmentaçãodeDados_Subscription_Type">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId5"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId6"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -39,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="323">
   <si>
     <t>Paleta de Cores</t>
   </si>
@@ -979,16 +993,47 @@
   </si>
   <si>
     <t>Subscription Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total de vendas dos planos anuais com as assinaturas agregadas, diferenciados por com auto renovação ou sem </t>
+  </si>
+  <si>
+    <t>Soma de Total Value</t>
+  </si>
+  <si>
+    <t>Rótulos de Linha</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t>XBOX GAME PASS SUBSCRIPTION SALES</t>
+  </si>
+  <si>
+    <t>Total de vendas dos planos da EA season</t>
+  </si>
+  <si>
+    <t>Soma de EA Play Season Pass</t>
+  </si>
+  <si>
+    <t>Total de vendas do Minecraft Season pass</t>
+  </si>
+  <si>
+    <t>Soma de Minecraft Season Pass Price</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1014,6 +1059,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1064,7 +1124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1081,13 +1141,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF22C55E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1108,36 +1177,59 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Título 1" xfId="1" builtinId="16"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="16">
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF22C55E"/>
+          <bgColor rgb="FF22C55E"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1182,12 +1274,17 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="SlicerStyleLight6 2" pivot="0" table="0" count="10" xr9:uid="{94B3A7D7-BEFA-45E1-AD24-292826E85154}">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <mruColors>
       <color rgb="FF22C55E"/>
+      <color rgb="FF5BF6A8"/>
       <color rgb="FFE8E6E9"/>
-      <color rgb="FF5BF6A8"/>
       <color rgb="FF000000"/>
       <color rgb="FFE0E0E0"/>
       <color rgb="FFEDEDED"/>
@@ -1198,14 +1295,1222 @@
     </mruColors>
   </colors>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{46F421CA-312F-682f-3DD2-61675219B42D}">
+      <x14:dxfs count="8">
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FFF8E162"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFFCF7E0"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="9" tint="0.79998168889431442"/>
+              <bgColor theme="9" tint="0.79998168889431442"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="9" tint="0.59999389629810485"/>
+              <bgColor theme="9" tint="0.59999389629810485"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFE0E0E0"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFE0E0E0"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFE0E0E0"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFE0E0E0"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+      </x14:dxfs>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1">
+        <x14:slicerStyle name="SlicerStyleLight6 2">
+          <x14:slicerStyleElements>
+            <x14:slicerStyleElement type="unselectedItemWithData" dxfId="7"/>
+            <x14:slicerStyleElement type="unselectedItemWithNoData" dxfId="6"/>
+            <x14:slicerStyleElement type="selectedItemWithData" dxfId="5"/>
+            <x14:slicerStyleElement type="selectedItemWithNoData" dxfId="4"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithData" dxfId="3"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithData" dxfId="2"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithNoData" dxfId="1"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithNoData" dxfId="0"/>
+          </x14:slicerStyleElements>
+        </x14:slicerStyle>
+      </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[dashboard_xbox.xlsx]C̳álculos!tbl_total_vendas</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="5BF6A8"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>C̳álculos!$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="5BF6A8"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>C̳álculos!$B$7:$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>No</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Yes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>C̳álculos!$C$7:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2824</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>747</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CB79-4F1F-AB62-2C7D655FCF48}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="393213920"/>
+        <c:axId val="309595440"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="393213920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="309595440"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="309595440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="393213920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="26">
+  <a:schemeClr val="accent6"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1948,8 +3253,5885 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>107570</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>140805</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>356907</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>115957</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EDB9617-D404-4474-8D65-67746BA8777D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="8663" t="23765" r="73597" b="23505"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2401853" y="331305"/>
+          <a:ext cx="489532" cy="521804"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38101</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2247901</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Subscription Type">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8A36B6D-82C3-4FA3-97EF-1B65EB55C060}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Subscription Type"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="38101" y="1692965"/>
+              <a:ext cx="2209800" cy="1260613"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>216176</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171037</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>442592</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>60464</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="6" name="Agrupar 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A68BBF27-AB80-E4C8-574E-537C45C6664A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2510459" y="3277015"/>
+          <a:ext cx="8260546" cy="2937427"/>
+          <a:chOff x="2428875" y="1323975"/>
+          <a:chExt cx="4619625" cy="2933700"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="Retângulo: Cantos Arredondados 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B919C3F8-465D-A996-8462-0847A0105843}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2428875" y="1323975"/>
+            <a:ext cx="4619625" cy="2933700"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 6566"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="pt-BR" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:graphicFrame macro="">
+        <xdr:nvGraphicFramePr>
+          <xdr:cNvPr id="4" name="Gráfico 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3632ECA4-0BD9-4481-8410-76476F80307A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGraphicFramePr>
+            <a:graphicFrameLocks/>
+          </xdr:cNvGraphicFramePr>
+        </xdr:nvGraphicFramePr>
+        <xdr:xfrm>
+          <a:off x="2446687" y="1418220"/>
+          <a:ext cx="4572000" cy="2743200"/>
+        </xdr:xfrm>
+        <a:graphic>
+          <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+            <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          </a:graphicData>
+        </a:graphic>
+      </xdr:graphicFrame>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>10768</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>104361</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>258940</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>103947</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="11" name="Agrupar 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{122575D9-E5DE-6782-7027-FAF852D98D86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2545246" y="1330187"/>
+          <a:ext cx="3925651" cy="1689238"/>
+          <a:chOff x="7456833" y="1388165"/>
+          <a:chExt cx="3925651" cy="1689238"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="7" name="Retângulo: Cantos Arredondados 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3805D65E-FEEE-C837-81DB-067462C2BAE1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7456833" y="1388165"/>
+            <a:ext cx="3922643" cy="1689238"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 11024"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="pt-BR" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="C̳álculos!D20">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="8" name="Retângulo: Cantos Arredondados 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E208846-2F20-27F0-2E78-B641096F8AD4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8975449" y="1920116"/>
+            <a:ext cx="2146852" cy="923925"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="5BF6A8"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:fld id="{2109E276-685F-4FC8-B602-20244C58B098}" type="TxLink">
+              <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:pPr algn="ctr"/>
+              <a:t>R$ 1.350,00</a:t>
+            </a:fld>
+            <a:endParaRPr lang="pt-BR" sz="2000" b="1">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="9" name="Retângulo: Cantos Superiores Arredondados 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98DBD50C-C276-06A7-9C32-2CDF794CD304}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7457836" y="1389669"/>
+            <a:ext cx="3924648" cy="384313"/>
+          </a:xfrm>
+          <a:prstGeom prst="round2SameRect">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 25829"/>
+              <a:gd name="adj2" fmla="val 0"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="22C55E"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1100" b="1">
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>TOTAL SUBSCRIPTIONS - EA</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1100" b="1" baseline="0">
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t> PLAY SEASON PASS</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1100" b="1">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="10" name="Imagem 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E652F8C-A30D-4A69-8262-3AEA06894632}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7711109" y="1772478"/>
+            <a:ext cx="1219200" cy="1219200"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>22363</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>115957</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>444471</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>115543</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="20" name="Agrupar 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04688177-EC2F-88E7-3E89-CFB12DB7062A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="6847233" y="1341783"/>
+          <a:ext cx="3925651" cy="1689238"/>
+          <a:chOff x="7460146" y="3371022"/>
+          <a:chExt cx="3925651" cy="1689238"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="13" name="Retângulo: Cantos Arredondados 12">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E59926AA-B8B5-0CF6-C36B-FC4C8ACEFE84}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7460146" y="3371022"/>
+            <a:ext cx="3922643" cy="1689238"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 11024"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="pt-BR" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="C̳álculos!D31">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="Retângulo: Cantos Arredondados 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FE5EAD9-AF9F-E8A4-368F-64B52265E762}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="9078154" y="3902973"/>
+            <a:ext cx="2146852" cy="923925"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="5BF6A8"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:fld id="{4D6FDBEF-58E8-44B4-89A5-45F11C701BE0}" type="TxLink">
+              <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>R$ 1.800,00</a:t>
+            </a:fld>
+            <a:endParaRPr lang="pt-BR" sz="2000" b="1">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="15" name="Retângulo: Cantos Superiores Arredondados 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BD7742D-21BB-515B-D094-6A3D405ED27E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7461149" y="3372526"/>
+            <a:ext cx="3924648" cy="384313"/>
+          </a:xfrm>
+          <a:prstGeom prst="round2SameRect">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 25829"/>
+              <a:gd name="adj2" fmla="val 0"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="22C55E"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1100" b="1">
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>TOTAL SUBSCRIPTIONS - MINECRAFT</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1100" b="1" baseline="0">
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t> SEASON PASS</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1100" b="1">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="17" name="Agrupar 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB7C5D0F-BFEF-43A7-84B8-6130290DC6A3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="7628284" y="4033631"/>
+            <a:ext cx="1364425" cy="662609"/>
+            <a:chOff x="3495675" y="5400674"/>
+            <a:chExt cx="1549476" cy="752476"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="18" name="Imagem 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34BF40F6-D5A0-46AC-8EE0-9B45881FB958}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+              <a:extLst>
+                <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                  <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3998608" y="5400674"/>
+              <a:ext cx="555497" cy="609599"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="19" name="Gráfico 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53DFC254-0A51-7903-E96B-E925FE110D9B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+              <a:extLst>
+                <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                  <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3495675" y="5895937"/>
+              <a:ext cx="1549476" cy="257213"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>216175</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171037</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>447260</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>174350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Retângulo: Cantos Superiores Arredondados 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{310E7613-0C56-429A-9B6B-7B889073DEA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2510458" y="3277015"/>
+          <a:ext cx="8265215" cy="384313"/>
+        </a:xfrm>
+        <a:prstGeom prst="round2SameRect">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 25829"/>
+            <a:gd name="adj2" fmla="val 0"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="22C55E"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100" b="1">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>TOTAL SUBSCRIPTIONS  XBOX GAME</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100" b="1" baseline="0">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> PASS</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1100" b="1">
+            <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>654223</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>59138</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1499153</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1264</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Elipse 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40AD8283-EB91-4750-B856-FC91E276B190}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="654223" y="249638"/>
+          <a:ext cx="844930" cy="844930"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </a:blipFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>496957</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>74543</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1231106" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="CaixaDeTexto 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2F731DF-5E45-EDD1-A493-C9C8F921DFC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="496957" y="1167847"/>
+          <a:ext cx="1231106" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Bem</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> vindo Fulano!</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>144117</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>28160</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4154727" cy="248851"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="CaixaDeTexto 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2126725-6F7E-0540-272C-6CEBAD765EAC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="914399"/>
+          <a:ext cx="4154727" cy="248851"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Calculation</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> period: 01/01/2024 - 31/12/24 | Last updated: 12/10/2026 - 15:16</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1000">
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Enzo Santiago de Souza" refreshedDate="46307.529465277781" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="295" xr:uid="{C670D251-A254-41E2-A8C5-58FBEE796449}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Tabela1"/>
+  </cacheSource>
+  <cacheFields count="13">
+    <cacheField name="Subscriber ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3231" maxValue="3525"/>
+    </cacheField>
+    <cacheField name="Name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Plan" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Ultimate"/>
+        <s v="Core"/>
+        <s v="Standard"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Start Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2024-12-17T00:00:00"/>
+    </cacheField>
+    <cacheField name="Auto Renewal" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Yes"/>
+        <s v="No"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Subscription Price" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="15"/>
+    </cacheField>
+    <cacheField name="Subscription Type" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Monthly"/>
+        <s v="Annual"/>
+        <s v="Quarterly"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="EA Play Season Pass" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="EA Play Season Pass_x000a_Price" numFmtId="44">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="30" maxValue="30"/>
+    </cacheField>
+    <cacheField name="Minecraft Season Pass" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Minecraft Season Pass Price" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="20"/>
+    </cacheField>
+    <cacheField name="Coupon Value" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="20"/>
+    </cacheField>
+    <cacheField name="Total Value" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="62"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="275523044"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="295">
+  <r>
+    <n v="3231"/>
+    <s v="João Silva"/>
+    <x v="0"/>
+    <d v="2024-01-01T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3232"/>
+    <s v="Maria Oliveira"/>
+    <x v="1"/>
+    <d v="2024-01-15T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3233"/>
+    <s v="Lucas Fernandes"/>
+    <x v="2"/>
+    <d v="2024-02-10T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3234"/>
+    <s v="Ana Souza"/>
+    <x v="0"/>
+    <d v="2024-02-20T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3235"/>
+    <s v="Pedro Gonçalves"/>
+    <x v="1"/>
+    <d v="2024-03-05T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3236"/>
+    <s v="Felipe Costa"/>
+    <x v="2"/>
+    <d v="2024-03-02T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="2"/>
+    <n v="28"/>
+  </r>
+  <r>
+    <n v="3237"/>
+    <s v="Camila Ribeiro"/>
+    <x v="0"/>
+    <d v="2024-03-03T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="55"/>
+  </r>
+  <r>
+    <n v="3238"/>
+    <s v="André Mendes"/>
+    <x v="1"/>
+    <d v="2024-03-04T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3239"/>
+    <s v="Sofia Almeida"/>
+    <x v="0"/>
+    <d v="2024-03-05T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3240"/>
+    <s v="Bruno Martins"/>
+    <x v="2"/>
+    <d v="2024-03-06T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3241"/>
+    <s v="Rita Castro"/>
+    <x v="1"/>
+    <d v="2024-03-07T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3242"/>
+    <s v="Marco Túlio"/>
+    <x v="0"/>
+    <d v="2024-03-08T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3243"/>
+    <s v="Lívia Silveira"/>
+    <x v="2"/>
+    <d v="2024-03-09T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3244"/>
+    <s v="Diogo Sousa"/>
+    <x v="1"/>
+    <d v="2024-03-10T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3245"/>
+    <s v="Fernanda Lima"/>
+    <x v="0"/>
+    <d v="2024-03-11T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="8"/>
+    <n v="57"/>
+  </r>
+  <r>
+    <n v="3246"/>
+    <s v="Caio Pereira"/>
+    <x v="2"/>
+    <d v="2024-03-12T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3247"/>
+    <s v="Beatriz Gomes"/>
+    <x v="1"/>
+    <d v="2024-03-13T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3248"/>
+    <s v="Cesar Oliveira"/>
+    <x v="0"/>
+    <d v="2024-03-14T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3249"/>
+    <s v="Débora Machado"/>
+    <x v="2"/>
+    <d v="2024-03-15T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <n v="3250"/>
+    <s v="Eduardo Vargas"/>
+    <x v="1"/>
+    <d v="2024-03-16T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3251"/>
+    <s v="Gabriela Santos"/>
+    <x v="0"/>
+    <d v="2024-03-17T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3252"/>
+    <s v="Henrique Dias"/>
+    <x v="2"/>
+    <d v="2024-03-18T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3253"/>
+    <s v="Isabela Moreira"/>
+    <x v="1"/>
+    <d v="2024-03-19T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3254"/>
+    <s v="Joaquim Barbosa"/>
+    <x v="0"/>
+    <d v="2024-03-20T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3255"/>
+    <s v="Lara Rocha"/>
+    <x v="2"/>
+    <d v="2024-03-21T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3256"/>
+    <s v="Matheus Silva"/>
+    <x v="1"/>
+    <d v="2024-03-22T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3257"/>
+    <s v="Nicole Costa"/>
+    <x v="0"/>
+    <d v="2024-03-23T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3258"/>
+    <s v="Otávio Mendonça"/>
+    <x v="2"/>
+    <d v="2024-03-24T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3259"/>
+    <s v="Paula Ferreira"/>
+    <x v="1"/>
+    <d v="2024-03-25T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3260"/>
+    <s v="Raquel Alves"/>
+    <x v="0"/>
+    <d v="2024-03-26T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3261"/>
+    <s v="Samuel Pires"/>
+    <x v="2"/>
+    <d v="2024-03-27T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3262"/>
+    <s v="Tânia Barros"/>
+    <x v="1"/>
+    <d v="2024-03-28T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3263"/>
+    <s v="Vinicius Lima"/>
+    <x v="0"/>
+    <d v="2024-03-29T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3264"/>
+    <s v="Yasmin Teixeira"/>
+    <x v="2"/>
+    <d v="2024-03-30T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3265"/>
+    <s v="Zé Carlos"/>
+    <x v="1"/>
+    <d v="2024-03-31T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3266"/>
+    <s v="Amanda Nogueira"/>
+    <x v="1"/>
+    <d v="2024-04-01T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3267"/>
+    <s v="Bruno Cavalheiro"/>
+    <x v="0"/>
+    <d v="2024-04-02T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3268"/>
+    <s v="Carla Dias"/>
+    <x v="2"/>
+    <d v="2024-04-03T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3269"/>
+    <s v="Diego Fontes"/>
+    <x v="1"/>
+    <d v="2024-04-04T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3270"/>
+    <s v="Eunice Lima"/>
+    <x v="0"/>
+    <d v="2024-04-05T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3271"/>
+    <s v="Fábio Martins"/>
+    <x v="2"/>
+    <d v="2024-04-06T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <n v="3272"/>
+    <s v="Gisele Araújo"/>
+    <x v="1"/>
+    <d v="2024-04-07T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3273"/>
+    <s v="Hélio Castro"/>
+    <x v="0"/>
+    <d v="2024-04-08T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3274"/>
+    <s v="Ingrid Menezes"/>
+    <x v="2"/>
+    <d v="2024-04-09T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3275"/>
+    <s v="Jorge Baptista"/>
+    <x v="1"/>
+    <d v="2024-04-10T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3276"/>
+    <s v="Kléber Oliveira"/>
+    <x v="0"/>
+    <d v="2024-04-11T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3277"/>
+    <s v="Luciana Freitas"/>
+    <x v="2"/>
+    <d v="2024-04-12T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3278"/>
+    <s v="Márcia Eller"/>
+    <x v="1"/>
+    <d v="2024-04-13T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3279"/>
+    <s v="Nilo Peçanha"/>
+    <x v="0"/>
+    <d v="2024-04-14T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3280"/>
+    <s v="Oscar Neves"/>
+    <x v="2"/>
+    <d v="2024-04-15T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3281"/>
+    <s v="Patrícia Soares"/>
+    <x v="1"/>
+    <d v="2024-04-16T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3282"/>
+    <s v="Quirino Gonçalves"/>
+    <x v="0"/>
+    <d v="2024-04-17T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3283"/>
+    <s v="Raul Machado"/>
+    <x v="2"/>
+    <d v="2024-04-18T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3284"/>
+    <s v="Sônia Lobo"/>
+    <x v="1"/>
+    <d v="2024-04-19T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3285"/>
+    <s v="Tiago Ramos"/>
+    <x v="0"/>
+    <d v="2024-04-20T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3286"/>
+    <s v="Ugo Pires"/>
+    <x v="2"/>
+    <d v="2024-04-21T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3287"/>
+    <s v="Valéria Nobre"/>
+    <x v="1"/>
+    <d v="2024-04-22T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3288"/>
+    <s v="William Siqueira"/>
+    <x v="0"/>
+    <d v="2024-04-23T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3289"/>
+    <s v="Xuxa Meneghel"/>
+    <x v="2"/>
+    <d v="2024-04-24T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3290"/>
+    <s v="Yara Figueiredo"/>
+    <x v="1"/>
+    <d v="2024-04-25T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3291"/>
+    <s v="Zacarias Alves"/>
+    <x v="0"/>
+    <d v="2024-04-26T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3292"/>
+    <s v="Amanda Bynes"/>
+    <x v="2"/>
+    <d v="2024-04-27T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3293"/>
+    <s v="Bruno Mars"/>
+    <x v="1"/>
+    <d v="2024-04-28T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3294"/>
+    <s v="Carla Bruni"/>
+    <x v="0"/>
+    <d v="2024-04-29T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3295"/>
+    <s v="Diego Maradona"/>
+    <x v="2"/>
+    <d v="2024-04-30T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <n v="3296"/>
+    <s v="Estela Marques"/>
+    <x v="1"/>
+    <d v="2024-05-01T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3297"/>
+    <s v="Fábio Nobre"/>
+    <x v="0"/>
+    <d v="2024-05-02T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3298"/>
+    <s v="Gabriel Oliveira"/>
+    <x v="2"/>
+    <d v="2024-05-03T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3299"/>
+    <s v="Helena Santos"/>
+    <x v="1"/>
+    <d v="2024-05-04T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3300"/>
+    <s v="Ivan Carvalho"/>
+    <x v="0"/>
+    <d v="2024-05-05T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3301"/>
+    <s v="Júlia Ferreira"/>
+    <x v="2"/>
+    <d v="2024-05-06T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <n v="3302"/>
+    <s v="Karla Alves"/>
+    <x v="1"/>
+    <d v="2024-05-07T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3303"/>
+    <s v="Lucas Mendes"/>
+    <x v="0"/>
+    <d v="2024-05-08T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3304"/>
+    <s v="Mônica Gomes"/>
+    <x v="2"/>
+    <d v="2024-05-09T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3305"/>
+    <s v="Norberto Queiroz"/>
+    <x v="1"/>
+    <d v="2024-05-10T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3306"/>
+    <s v="Otávio Barros"/>
+    <x v="0"/>
+    <d v="2024-05-11T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3307"/>
+    <s v="Paula Vieira"/>
+    <x v="2"/>
+    <d v="2024-05-12T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3308"/>
+    <s v="Quentin Ramos"/>
+    <x v="1"/>
+    <d v="2024-05-13T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3309"/>
+    <s v="Raquel Novaes"/>
+    <x v="0"/>
+    <d v="2024-05-14T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3310"/>
+    <s v="Samantha Lopes"/>
+    <x v="2"/>
+    <d v="2024-05-15T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3311"/>
+    <s v="Tiago Martins"/>
+    <x v="1"/>
+    <d v="2024-05-16T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3312"/>
+    <s v="Ulysses Guimarães"/>
+    <x v="0"/>
+    <d v="2024-05-17T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3313"/>
+    <s v="Vanessa Silva"/>
+    <x v="2"/>
+    <d v="2024-05-18T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3314"/>
+    <s v="William Carneiro"/>
+    <x v="1"/>
+    <d v="2024-05-19T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3315"/>
+    <s v="Ximena Rocha"/>
+    <x v="0"/>
+    <d v="2024-05-20T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3316"/>
+    <s v="Yasmin Figueiredo"/>
+    <x v="2"/>
+    <d v="2024-05-21T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3317"/>
+    <s v="Zara Cunha"/>
+    <x v="1"/>
+    <d v="2024-05-22T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3318"/>
+    <s v="Alan Teixeira"/>
+    <x v="0"/>
+    <d v="2024-05-23T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3319"/>
+    <s v="Bárbara Oliveira"/>
+    <x v="2"/>
+    <d v="2024-05-24T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3320"/>
+    <s v="Carlos Junqueira"/>
+    <x v="1"/>
+    <d v="2024-05-25T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3321"/>
+    <s v="Daniela Moura"/>
+    <x v="0"/>
+    <d v="2024-05-26T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3322"/>
+    <s v="Eduardo Lima"/>
+    <x v="2"/>
+    <d v="2024-05-27T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3323"/>
+    <s v="Fabiana Araújo"/>
+    <x v="1"/>
+    <d v="2024-05-28T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3324"/>
+    <s v="Geraldo Ribeiro"/>
+    <x v="0"/>
+    <d v="2024-05-29T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3325"/>
+    <s v="Héctor Vargas"/>
+    <x v="2"/>
+    <d v="2024-05-30T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3326"/>
+    <s v="Isabela Fonseca"/>
+    <x v="1"/>
+    <d v="2024-05-31T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3327"/>
+    <s v="João Pedro Almeida"/>
+    <x v="0"/>
+    <d v="2024-06-01T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3328"/>
+    <s v="Klara Costa"/>
+    <x v="2"/>
+    <d v="2024-06-02T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3329"/>
+    <s v="Luciana Mendes"/>
+    <x v="1"/>
+    <d v="2024-06-03T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3330"/>
+    <s v="Marcelo Gouveia"/>
+    <x v="0"/>
+    <d v="2024-06-04T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3331"/>
+    <s v="Nívea Borges"/>
+    <x v="2"/>
+    <d v="2024-06-05T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <n v="3332"/>
+    <s v="Oscar Nogueira"/>
+    <x v="1"/>
+    <d v="2024-06-06T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3333"/>
+    <s v="Patrícia Alves"/>
+    <x v="0"/>
+    <d v="2024-06-07T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3334"/>
+    <s v="Rafaela Silva"/>
+    <x v="2"/>
+    <d v="2024-06-08T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3335"/>
+    <s v="Samantha Moraes"/>
+    <x v="1"/>
+    <d v="2024-06-09T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3336"/>
+    <s v="Tatiana Rocha"/>
+    <x v="1"/>
+    <d v="2024-06-10T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3337"/>
+    <s v="Ulisses Tavares"/>
+    <x v="0"/>
+    <d v="2024-06-11T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3338"/>
+    <s v="Víctor Lemos"/>
+    <x v="2"/>
+    <d v="2024-06-12T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3339"/>
+    <s v="Wilma Barros"/>
+    <x v="1"/>
+    <d v="2024-06-13T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3340"/>
+    <s v="Xavier Nascimento"/>
+    <x v="0"/>
+    <d v="2024-06-14T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3341"/>
+    <s v="Yago Pereira"/>
+    <x v="2"/>
+    <d v="2024-06-15T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <n v="3342"/>
+    <s v="Zilda Ferreira"/>
+    <x v="1"/>
+    <d v="2024-06-16T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3343"/>
+    <s v="Amanda Lopes"/>
+    <x v="0"/>
+    <d v="2024-06-17T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3344"/>
+    <s v="Bruno Miranda"/>
+    <x v="2"/>
+    <d v="2024-06-18T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3345"/>
+    <s v="Célia Torres"/>
+    <x v="1"/>
+    <d v="2024-06-19T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3346"/>
+    <s v="Diogo Souza"/>
+    <x v="0"/>
+    <d v="2024-06-20T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3347"/>
+    <s v="Elisa Castro"/>
+    <x v="2"/>
+    <d v="2024-06-21T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3348"/>
+    <s v="Fátima Lima"/>
+    <x v="1"/>
+    <d v="2024-06-22T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3349"/>
+    <s v="Geraldo Ribeiro"/>
+    <x v="0"/>
+    <d v="2024-06-23T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3350"/>
+    <s v="Hélio Martins"/>
+    <x v="2"/>
+    <d v="2024-06-24T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3351"/>
+    <s v="Íris Santos"/>
+    <x v="1"/>
+    <d v="2024-06-25T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3352"/>
+    <s v="João Marcelo"/>
+    <x v="0"/>
+    <d v="2024-06-26T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3353"/>
+    <s v="Larissa Gomes"/>
+    <x v="2"/>
+    <d v="2024-06-27T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3354"/>
+    <s v="Márcio Silva"/>
+    <x v="1"/>
+    <d v="2024-06-28T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3355"/>
+    <s v="Nadia Costa"/>
+    <x v="0"/>
+    <d v="2024-06-29T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3356"/>
+    <s v="Oscar Almeida"/>
+    <x v="2"/>
+    <d v="2024-06-30T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3357"/>
+    <s v="Patricia Soares"/>
+    <x v="1"/>
+    <d v="2024-07-01T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3358"/>
+    <s v="Quênia Barros"/>
+    <x v="0"/>
+    <d v="2024-07-02T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3359"/>
+    <s v="Rafael Torres"/>
+    <x v="2"/>
+    <d v="2024-07-03T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3360"/>
+    <s v="Silvia Nascimento"/>
+    <x v="1"/>
+    <d v="2024-07-04T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3361"/>
+    <s v="Tiago Mendes"/>
+    <x v="0"/>
+    <d v="2024-07-05T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3362"/>
+    <s v="Ursula Silva"/>
+    <x v="2"/>
+    <d v="2024-07-06T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3363"/>
+    <s v="Vanessa Moraes"/>
+    <x v="1"/>
+    <d v="2024-07-07T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3364"/>
+    <s v="Waldir Junior"/>
+    <x v="0"/>
+    <d v="2024-07-08T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3365"/>
+    <s v="Xavier Lopes"/>
+    <x v="2"/>
+    <d v="2024-07-09T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3366"/>
+    <s v="Yolanda Freitas"/>
+    <x v="1"/>
+    <d v="2024-07-10T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3367"/>
+    <s v="Zacarias Nunes"/>
+    <x v="0"/>
+    <d v="2024-07-11T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3368"/>
+    <s v="Ana Clara Barreto"/>
+    <x v="2"/>
+    <d v="2024-07-12T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3369"/>
+    <s v="Bruno Henrique"/>
+    <x v="1"/>
+    <d v="2024-07-13T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3370"/>
+    <s v="Carlos Eduardo"/>
+    <x v="0"/>
+    <d v="2024-07-14T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3371"/>
+    <s v="Débora Lima"/>
+    <x v="2"/>
+    <d v="2024-07-15T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <n v="3372"/>
+    <s v="Elisa Neves"/>
+    <x v="1"/>
+    <d v="2024-07-16T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3373"/>
+    <s v="Fabiano Gomes"/>
+    <x v="0"/>
+    <d v="2024-07-17T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3374"/>
+    <s v="Gisele Oliveira"/>
+    <x v="2"/>
+    <d v="2024-07-18T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3375"/>
+    <s v="Héctor Silva"/>
+    <x v="1"/>
+    <d v="2024-07-19T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3376"/>
+    <s v="Igor Martins"/>
+    <x v="0"/>
+    <d v="2024-07-20T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3377"/>
+    <s v="Joana Figueiredo"/>
+    <x v="2"/>
+    <d v="2024-07-21T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3378"/>
+    <s v="Kleber Machado"/>
+    <x v="1"/>
+    <d v="2024-07-22T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3379"/>
+    <s v="Luciana Santos"/>
+    <x v="0"/>
+    <d v="2024-07-23T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3380"/>
+    <s v="Marcos Teixeira"/>
+    <x v="2"/>
+    <d v="2024-07-24T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3381"/>
+    <s v="Natalia Costa"/>
+    <x v="1"/>
+    <d v="2024-07-25T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3382"/>
+    <s v="Oscar Ribeiro"/>
+    <x v="0"/>
+    <d v="2024-07-26T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3383"/>
+    <s v="Patricia Almeida"/>
+    <x v="2"/>
+    <d v="2024-07-27T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3384"/>
+    <s v="Quirino Junior"/>
+    <x v="1"/>
+    <d v="2024-07-28T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3385"/>
+    <s v="Renata Machado"/>
+    <x v="0"/>
+    <d v="2024-07-29T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3386"/>
+    <s v="Sônia Alves"/>
+    <x v="2"/>
+    <d v="2024-07-30T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3387"/>
+    <s v="Tiago Nunes"/>
+    <x v="1"/>
+    <d v="2024-07-31T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3388"/>
+    <s v="Ulysses Pereira"/>
+    <x v="0"/>
+    <d v="2024-08-01T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3389"/>
+    <s v="Vanessa Lima"/>
+    <x v="2"/>
+    <d v="2024-08-02T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3390"/>
+    <s v="Wagner Santos"/>
+    <x v="1"/>
+    <d v="2024-08-03T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3391"/>
+    <s v="Xuxa Meneghel"/>
+    <x v="0"/>
+    <d v="2024-08-04T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3392"/>
+    <s v="Yasmin Silva"/>
+    <x v="2"/>
+    <d v="2024-08-05T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3393"/>
+    <s v="Zacarias de Souza"/>
+    <x v="1"/>
+    <d v="2024-08-06T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3394"/>
+    <s v="André Lima"/>
+    <x v="0"/>
+    <d v="2024-08-07T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3395"/>
+    <s v="Bianca Freitas"/>
+    <x v="2"/>
+    <d v="2024-08-08T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3396"/>
+    <s v="Caio Mendes"/>
+    <x v="1"/>
+    <d v="2024-08-09T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3397"/>
+    <s v="Daniela Moura"/>
+    <x v="0"/>
+    <d v="2024-08-10T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3398"/>
+    <s v="Eduardo Costa"/>
+    <x v="2"/>
+    <d v="2024-08-11T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3399"/>
+    <s v="Fernanda Gomes"/>
+    <x v="1"/>
+    <d v="2024-08-12T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3400"/>
+    <s v="Guilherme Souza"/>
+    <x v="0"/>
+    <d v="2024-08-13T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3401"/>
+    <s v="Helena Ribeiro"/>
+    <x v="2"/>
+    <d v="2024-08-14T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3402"/>
+    <s v="Igor Santos"/>
+    <x v="1"/>
+    <d v="2024-08-15T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3403"/>
+    <s v="João Carvalho"/>
+    <x v="0"/>
+    <d v="2024-08-16T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3404"/>
+    <s v="Klara Fagundes"/>
+    <x v="2"/>
+    <d v="2024-08-17T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3405"/>
+    <s v="Lúcia Mendonça"/>
+    <x v="1"/>
+    <d v="2024-08-18T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3406"/>
+    <s v="Marcelo Novaes"/>
+    <x v="1"/>
+    <d v="2024-08-19T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3407"/>
+    <s v="Nina Pacheco"/>
+    <x v="0"/>
+    <d v="2024-08-20T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3408"/>
+    <s v="Olívia Rios"/>
+    <x v="2"/>
+    <d v="2024-08-21T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3409"/>
+    <s v="Paulo Quintana"/>
+    <x v="1"/>
+    <d v="2024-08-22T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3410"/>
+    <s v="Raquel Domingos"/>
+    <x v="0"/>
+    <d v="2024-08-23T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3411"/>
+    <s v="Samuel Viana"/>
+    <x v="2"/>
+    <d v="2024-08-24T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <n v="3412"/>
+    <s v="Tatiane Rocha"/>
+    <x v="1"/>
+    <d v="2024-08-25T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3413"/>
+    <s v="Ulysses Farias"/>
+    <x v="0"/>
+    <d v="2024-08-26T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3414"/>
+    <s v="Vanessa Moreira"/>
+    <x v="2"/>
+    <d v="2024-08-27T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3415"/>
+    <s v="William Carvalho"/>
+    <x v="1"/>
+    <d v="2024-08-28T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3416"/>
+    <s v="Ximena Barros"/>
+    <x v="0"/>
+    <d v="2024-08-29T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3417"/>
+    <s v="Yara Machado"/>
+    <x v="2"/>
+    <d v="2024-08-30T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3418"/>
+    <s v="Zacarias Costa"/>
+    <x v="1"/>
+    <d v="2024-08-31T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3419"/>
+    <s v="André Lopes"/>
+    <x v="0"/>
+    <d v="2024-09-01T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3420"/>
+    <s v="Beatriz Souza"/>
+    <x v="2"/>
+    <d v="2024-09-02T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3421"/>
+    <s v="Caio Pereira"/>
+    <x v="1"/>
+    <d v="2024-09-03T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3422"/>
+    <s v="Daniela Araújo"/>
+    <x v="0"/>
+    <d v="2024-09-04T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3423"/>
+    <s v="Eduardo Santos"/>
+    <x v="2"/>
+    <d v="2024-09-05T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3424"/>
+    <s v="Fernanda Lima"/>
+    <x v="1"/>
+    <d v="2024-09-06T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3425"/>
+    <s v="Gabriel Teixeira"/>
+    <x v="0"/>
+    <d v="2024-09-07T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3426"/>
+    <s v="Helena Ribeiro"/>
+    <x v="2"/>
+    <d v="2024-09-08T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3427"/>
+    <s v="Igor Mendes"/>
+    <x v="1"/>
+    <d v="2024-09-09T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3428"/>
+    <s v="Joana Silveira"/>
+    <x v="0"/>
+    <d v="2024-09-10T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3429"/>
+    <s v="Lucas Martins"/>
+    <x v="2"/>
+    <d v="2024-09-11T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3430"/>
+    <s v="Marcela Gouveia"/>
+    <x v="1"/>
+    <d v="2024-09-12T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3431"/>
+    <s v="Nicolas Borges"/>
+    <x v="0"/>
+    <d v="2024-09-13T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3432"/>
+    <s v="Olivia Freitas"/>
+    <x v="2"/>
+    <d v="2024-09-14T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3433"/>
+    <s v="Paulo Nogueira"/>
+    <x v="1"/>
+    <d v="2024-09-15T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3434"/>
+    <s v="Raquel Andrade"/>
+    <x v="0"/>
+    <d v="2024-09-16T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3435"/>
+    <s v="Sônia Carvalho"/>
+    <x v="2"/>
+    <d v="2024-09-17T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3436"/>
+    <s v="Tiago Rodrigues"/>
+    <x v="1"/>
+    <d v="2024-09-18T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3437"/>
+    <s v="Ursula Monteiro"/>
+    <x v="0"/>
+    <d v="2024-09-19T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3438"/>
+    <s v="Vanessa Pereira"/>
+    <x v="2"/>
+    <d v="2024-09-20T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3439"/>
+    <s v="Walter Silva"/>
+    <x v="1"/>
+    <d v="2024-09-21T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3440"/>
+    <s v="Xavier Almeida"/>
+    <x v="0"/>
+    <d v="2024-09-22T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3441"/>
+    <s v="Yasmine Correia"/>
+    <x v="2"/>
+    <d v="2024-09-23T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <n v="3442"/>
+    <s v="Zacarias Almeida"/>
+    <x v="1"/>
+    <d v="2024-09-24T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3443"/>
+    <s v="Amanda Costa"/>
+    <x v="0"/>
+    <d v="2024-09-25T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3444"/>
+    <s v="Bruno Ferreira"/>
+    <x v="2"/>
+    <d v="2024-09-26T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3445"/>
+    <s v="Carla Dias"/>
+    <x v="1"/>
+    <d v="2024-09-27T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3446"/>
+    <s v="Diogo Martins"/>
+    <x v="0"/>
+    <d v="2024-09-28T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3447"/>
+    <s v="Elisa Campos"/>
+    <x v="2"/>
+    <d v="2024-09-29T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3448"/>
+    <s v="Fabiana Lima"/>
+    <x v="1"/>
+    <d v="2024-09-30T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3449"/>
+    <s v="Gabriel Santos"/>
+    <x v="0"/>
+    <d v="2024-10-01T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3450"/>
+    <s v="Helena Ferreira"/>
+    <x v="2"/>
+    <d v="2024-10-02T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3451"/>
+    <s v="Ígor Nunes"/>
+    <x v="1"/>
+    <d v="2024-10-03T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3452"/>
+    <s v="Joana Silveira"/>
+    <x v="0"/>
+    <d v="2024-10-04T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3453"/>
+    <s v="Kléber Oliveira"/>
+    <x v="2"/>
+    <d v="2024-10-05T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3454"/>
+    <s v="Luciana Morais"/>
+    <x v="1"/>
+    <d v="2024-10-06T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3455"/>
+    <s v="Marcos Vinícius"/>
+    <x v="0"/>
+    <d v="2024-10-07T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3456"/>
+    <s v="Natália Barros"/>
+    <x v="2"/>
+    <d v="2024-10-08T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3457"/>
+    <s v="Oscar Sampaio"/>
+    <x v="1"/>
+    <d v="2024-10-09T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3458"/>
+    <s v="Patrícia Leite"/>
+    <x v="0"/>
+    <d v="2024-10-10T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3459"/>
+    <s v="Quênia Rocha"/>
+    <x v="2"/>
+    <d v="2024-10-11T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3460"/>
+    <s v="Rafael Torres"/>
+    <x v="1"/>
+    <d v="2024-10-12T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3461"/>
+    <s v="Sandra Gouveia"/>
+    <x v="0"/>
+    <d v="2024-10-13T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3462"/>
+    <s v="Tiago Lacerda"/>
+    <x v="2"/>
+    <d v="2024-10-14T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3463"/>
+    <s v="Ursula Fonseca"/>
+    <x v="1"/>
+    <d v="2024-10-15T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3464"/>
+    <s v="Vanessa Andrade"/>
+    <x v="0"/>
+    <d v="2024-10-16T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3465"/>
+    <s v="William Castro"/>
+    <x v="2"/>
+    <d v="2024-10-17T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3466"/>
+    <s v="Xavier Monteiro"/>
+    <x v="1"/>
+    <d v="2024-10-18T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3467"/>
+    <s v="Yasmin Figueira"/>
+    <x v="0"/>
+    <d v="2024-10-19T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3468"/>
+    <s v="Zacarias Mendonça"/>
+    <x v="2"/>
+    <d v="2024-10-20T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3469"/>
+    <s v="Amanda Menezes"/>
+    <x v="1"/>
+    <d v="2024-10-21T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3470"/>
+    <s v="Bruno Santos"/>
+    <x v="0"/>
+    <d v="2024-10-22T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3471"/>
+    <s v="Carla Ferreira"/>
+    <x v="2"/>
+    <d v="2024-10-23T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3472"/>
+    <s v="Diogo Alves"/>
+    <x v="1"/>
+    <d v="2024-10-24T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3473"/>
+    <s v="Elisa Neves"/>
+    <x v="0"/>
+    <d v="2024-10-25T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3474"/>
+    <s v="Fabiano Pires"/>
+    <x v="2"/>
+    <d v="2024-10-26T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3475"/>
+    <s v="Giovana Ribeiro"/>
+    <x v="1"/>
+    <d v="2024-10-27T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3476"/>
+    <s v="Hélio Costa"/>
+    <x v="0"/>
+    <d v="2024-10-28T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3477"/>
+    <s v="Íris Loureiro"/>
+    <x v="2"/>
+    <d v="2024-10-29T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3478"/>
+    <s v="João Pereira"/>
+    <x v="1"/>
+    <d v="2024-10-30T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3479"/>
+    <s v="Klara Silva"/>
+    <x v="0"/>
+    <d v="2024-10-31T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3480"/>
+    <s v="Luciana Barros"/>
+    <x v="2"/>
+    <d v="2024-11-01T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3481"/>
+    <s v="Marcos Gomes"/>
+    <x v="1"/>
+    <d v="2024-11-02T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3482"/>
+    <s v="Natália Soares"/>
+    <x v="0"/>
+    <d v="2024-11-03T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3483"/>
+    <s v="Oscar Machado"/>
+    <x v="2"/>
+    <d v="2024-11-04T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3484"/>
+    <s v="Patrícia Lima"/>
+    <x v="1"/>
+    <d v="2024-11-05T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3485"/>
+    <s v="Quirino Neto"/>
+    <x v="0"/>
+    <d v="2024-11-06T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3486"/>
+    <s v="Rafaela Souza"/>
+    <x v="1"/>
+    <d v="2024-11-07T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3487"/>
+    <s v="Sandro Almeida"/>
+    <x v="0"/>
+    <d v="2024-11-08T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3488"/>
+    <s v="Tânia Ribeiro"/>
+    <x v="2"/>
+    <d v="2024-11-09T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3489"/>
+    <s v="Ugo Dias"/>
+    <x v="1"/>
+    <d v="2024-11-10T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3490"/>
+    <s v="Valéria Lima"/>
+    <x v="0"/>
+    <d v="2024-11-11T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3491"/>
+    <s v="William Fernandes"/>
+    <x v="2"/>
+    <d v="2024-11-12T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="25"/>
+  </r>
+  <r>
+    <n v="3492"/>
+    <s v="Xuxa Mendes"/>
+    <x v="1"/>
+    <d v="2024-11-13T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3493"/>
+    <s v="Ygor Farias"/>
+    <x v="0"/>
+    <d v="2024-11-14T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3494"/>
+    <s v="Zilda Barros"/>
+    <x v="2"/>
+    <d v="2024-11-15T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3495"/>
+    <s v="Amanda Santos"/>
+    <x v="1"/>
+    <d v="2024-11-16T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3496"/>
+    <s v="Bruno Costa"/>
+    <x v="0"/>
+    <d v="2024-11-17T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3497"/>
+    <s v="Carla Rodrigues"/>
+    <x v="2"/>
+    <d v="2024-11-18T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3498"/>
+    <s v="Diogo Pereira"/>
+    <x v="1"/>
+    <d v="2024-11-19T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3499"/>
+    <s v="Elisa Correia"/>
+    <x v="0"/>
+    <d v="2024-11-20T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3500"/>
+    <s v="Fábio Lourenço"/>
+    <x v="2"/>
+    <d v="2024-11-21T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3501"/>
+    <s v="Gabriela Neves"/>
+    <x v="1"/>
+    <d v="2024-11-22T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3502"/>
+    <s v="Henrique Gonçalves"/>
+    <x v="0"/>
+    <d v="2024-11-23T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3503"/>
+    <s v="Íris Santos"/>
+    <x v="2"/>
+    <d v="2024-11-24T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3504"/>
+    <s v="João Marcelo Alves"/>
+    <x v="1"/>
+    <d v="2024-11-25T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3505"/>
+    <s v="Klara Fonseca"/>
+    <x v="0"/>
+    <d v="2024-11-26T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3506"/>
+    <s v="Lucas Mendonça"/>
+    <x v="2"/>
+    <d v="2024-11-27T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3507"/>
+    <s v="Marcela Torres"/>
+    <x v="1"/>
+    <d v="2024-11-28T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3508"/>
+    <s v="Natália Castro"/>
+    <x v="0"/>
+    <d v="2024-11-29T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3509"/>
+    <s v="Oscar Martins"/>
+    <x v="2"/>
+    <d v="2024-11-30T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3510"/>
+    <s v="Patrícia Oliveira"/>
+    <x v="1"/>
+    <d v="2024-12-01T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3511"/>
+    <s v="Quentin Nogueira"/>
+    <x v="0"/>
+    <d v="2024-12-02T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <n v="3512"/>
+    <s v="Raquel Silva"/>
+    <x v="2"/>
+    <d v="2024-12-03T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3513"/>
+    <s v="Sandro Gomes"/>
+    <x v="1"/>
+    <d v="2024-12-04T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <n v="3514"/>
+    <s v="Tânia Machado"/>
+    <x v="0"/>
+    <d v="2024-12-05T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="2"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="7"/>
+    <n v="58"/>
+  </r>
+  <r>
+    <n v="3515"/>
+    <s v="Ursula Silva"/>
+    <x v="2"/>
+    <d v="2024-12-06T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3516"/>
+    <s v="Vanessa Moraes"/>
+    <x v="1"/>
+    <d v="2024-12-07T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3517"/>
+    <s v="William Carvalho"/>
+    <x v="0"/>
+    <d v="2024-12-08T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="20"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <n v="3518"/>
+    <s v="Xavier Reis"/>
+    <x v="2"/>
+    <d v="2024-12-09T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="12"/>
+    <n v="18"/>
+  </r>
+  <r>
+    <n v="3519"/>
+    <s v="Yasmin Rocha"/>
+    <x v="1"/>
+    <d v="2024-12-10T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <n v="3520"/>
+    <s v="Zacarias Duarte"/>
+    <x v="0"/>
+    <d v="2024-12-11T00:00:00"/>
+    <x v="0"/>
+    <n v="15"/>
+    <x v="1"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="5"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <n v="3521"/>
+    <s v="Amanda Freitas"/>
+    <x v="2"/>
+    <d v="2024-12-12T00:00:00"/>
+    <x v="1"/>
+    <n v="10"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="10"/>
+    <n v="20"/>
+  </r>
+  <r>
+    <n v="3522"/>
+    <s v="Bruno Almeida"/>
+    <x v="1"/>
+    <d v="2024-12-13T00:00:00"/>
+    <x v="0"/>
+    <n v="5"/>
+    <x v="2"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <n v="3523"/>
+    <s v="Carla Siqueira"/>
+    <x v="0"/>
+    <d v="2024-12-14T00:00:00"/>
+    <x v="1"/>
+    <n v="15"/>
+    <x v="0"/>
+    <s v="Yes"/>
+    <n v="30"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="3"/>
+    <n v="62"/>
+  </r>
+  <r>
+    <n v="3524"/>
+    <s v="Diogo Ramos"/>
+    <x v="2"/>
+    <d v="2024-12-15T00:00:00"/>
+    <x v="0"/>
+    <n v="10"/>
+    <x v="1"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="Yes"/>
+    <n v="20"/>
+    <n v="15"/>
+    <n v="15"/>
+  </r>
+  <r>
+    <n v="3525"/>
+    <s v="Elisa Magalhães"/>
+    <x v="1"/>
+    <d v="2024-12-16T00:00:00"/>
+    <x v="1"/>
+    <n v="5"/>
+    <x v="0"/>
+    <s v="No"/>
+    <s v="-"/>
+    <s v="No"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{36D2D5C7-09A5-4FBE-97B1-7392E0CE49C8}" name="Tabela dinâmica3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="B27:C31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de Minecraft Season Pass Price" fld="10" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BA1AC406-4F05-4F65-BA24-0444286EE028}" name="Tabela dinâmica2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="B16:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de EA Play Season Pass" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DB2FB12-7B84-4A88-AF28-5D009C1C03C7}" name="tbl_total_vendas" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="B6:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de Total Value" fld="12" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Subscription_Type" xr10:uid="{B8DA368F-88B6-43DE-8683-E661E66FDF47}" sourceName="Subscription Type">
+  <pivotTables>
+    <pivotTable tabId="3" name="tbl_total_vendas"/>
+    <pivotTable tabId="3" name="Tabela dinâmica2"/>
+    <pivotTable tabId="3" name="Tabela dinâmica3"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="275523044">
+      <items count="3">
+        <i x="1"/>
+        <i x="0" s="1"/>
+        <i x="2"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Subscription Type" xr10:uid="{A5D5F419-5DDA-4CD4-9CD4-AB5DCAE62FBB}" cache="SegmentaçãodeDados_Subscription_Type" caption="Subscription Type" style="SlicerStyleLight6 2" rowHeight="257175"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}" name="Tabela1" displayName="Tabela1" ref="A1:M296" totalsRowShown="0" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}" name="Tabela1" displayName="Tabela1" ref="A1:M296" totalsRowShown="0" dataDxfId="15">
   <autoFilter ref="A1:M296" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}">
     <filterColumn colId="7">
       <filters>
@@ -1958,19 +9140,19 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C4A90516-688A-46BF-9167-EA16C2A8A652}" name="Subscriber ID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{53DD39D0-2220-4121-9E9D-4EAA7E151C0F}" name="Name" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{4F5FF271-4C57-4BE0-8F2C-F82C8551625C}" name="Plan" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{8C17EB93-79B9-4E55-B8F7-BEB82F8253E9}" name="Start Date" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{48CEDF9B-1689-482A-A828-5CCE7713264A}" name="Auto Renewal" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{78B82374-9AA7-4E38-AE4F-78CDE6C83720}" name="Subscription Price" dataDxfId="15" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{F2433F68-AF33-49D0-B1FB-19A396074EDE}" name="Subscription Type" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{FD4D9C95-F6E5-4933-9068-A71FF7DF9343}" name="EA Play Season Pass" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{978DD0D2-834E-4CE4-A39B-30976086932F}" name="EA Play Season Pass_x000a_Price" dataDxfId="12" dataCellStyle="Moeda"/>
-    <tableColumn id="9" xr3:uid="{6E29F111-C395-4580-9DAD-3407D9E8B1A4}" name="Minecraft Season Pass" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{EF544EAA-7F25-4FD5-A10E-8E62804DB9E3}" name="Minecraft Season Pass Price" dataDxfId="10" dataCellStyle="Moeda"/>
-    <tableColumn id="11" xr3:uid="{7F6EB64A-1F07-4E48-9F0F-AC7D9DCD26F8}" name="Coupon Value" dataDxfId="9" dataCellStyle="Moeda"/>
-    <tableColumn id="12" xr3:uid="{2B04ABC8-DE6F-426E-ADC0-D8AFC68CA58E}" name="Total Value" dataDxfId="8" dataCellStyle="Moeda"/>
+    <tableColumn id="1" xr3:uid="{C4A90516-688A-46BF-9167-EA16C2A8A652}" name="Subscriber ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{53DD39D0-2220-4121-9E9D-4EAA7E151C0F}" name="Name" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{4F5FF271-4C57-4BE0-8F2C-F82C8551625C}" name="Plan" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{8C17EB93-79B9-4E55-B8F7-BEB82F8253E9}" name="Start Date" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{48CEDF9B-1689-482A-A828-5CCE7713264A}" name="Auto Renewal" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{78B82374-9AA7-4E38-AE4F-78CDE6C83720}" name="Subscription Price" dataDxfId="9" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{F2433F68-AF33-49D0-B1FB-19A396074EDE}" name="Subscription Type" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{FD4D9C95-F6E5-4933-9068-A71FF7DF9343}" name="EA Play Season Pass" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{978DD0D2-834E-4CE4-A39B-30976086932F}" name="EA Play Season Pass_x000a_Price" dataDxfId="6" dataCellStyle="Moeda"/>
+    <tableColumn id="9" xr3:uid="{6E29F111-C395-4580-9DAD-3407D9E8B1A4}" name="Minecraft Season Pass" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{EF544EAA-7F25-4FD5-A10E-8E62804DB9E3}" name="Minecraft Season Pass Price" dataDxfId="4" dataCellStyle="Moeda"/>
+    <tableColumn id="11" xr3:uid="{7F6EB64A-1F07-4E48-9F0F-AC7D9DCD26F8}" name="Coupon Value" dataDxfId="3" dataCellStyle="Moeda"/>
+    <tableColumn id="12" xr3:uid="{2B04ABC8-DE6F-426E-ADC0-D8AFC68CA58E}" name="Total Value" dataDxfId="2" dataCellStyle="Moeda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2296,7 +9478,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
-  <dimension ref="B3:P21"/>
+  <dimension ref="B3:P31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="3.5703125" customWidth="1"/>
@@ -2452,6 +9634,11 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>313</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -14632,10 +21819,11 @@
   <sheetPr>
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="B2:D31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.28515625" customWidth="1"/>
     <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
@@ -14647,34 +21835,523 @@
     <col min="16" max="16" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="C6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="12">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="12">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="12">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="14" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="16">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="C20" s="16">
+        <v>1350</v>
+      </c>
+      <c r="D20" s="17">
+        <f>GETPIVOTDATA("EA Play Season Pass
+Price",$B$16)</f>
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="14" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="C27" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="12">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="12">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="C31" s="12">
+        <v>1800</v>
+      </c>
+      <c r="D31" s="18">
+        <f>GETPIVOTDATA("Minecraft Season Pass Price",$B$27)</f>
+        <v>1800</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210F14EF-C0B7-459D-9E09-3130BA4314A6}">
-  <dimension ref="A2:A7"/>
+  <dimension ref="A2:I101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" style="4" customWidth="1"/>
     <col min="2" max="2" width="3.5703125" customWidth="1"/>
     <col min="12" max="12" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:9" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C2" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" spans="1:9" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+    </row>
+    <row r="6" spans="1:9" s="7" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" s="7" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" s="7" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+    </row>
+    <row r="11" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+    </row>
+    <row r="17" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+    </row>
+    <row r="18" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+    </row>
+    <row r="19" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+    </row>
+    <row r="20" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+    </row>
+    <row r="21" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+    </row>
+    <row r="22" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+    </row>
+    <row r="23" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+    </row>
+    <row r="24" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+    </row>
+    <row r="25" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+    </row>
+    <row r="26" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+    </row>
+    <row r="27" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+    </row>
+    <row r="28" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+    </row>
+    <row r="29" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+    </row>
+    <row r="30" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+    </row>
+    <row r="31" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+    </row>
+    <row r="32" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+    </row>
+    <row r="33" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+    </row>
+    <row r="34" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+    </row>
+    <row r="35" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+    </row>
+    <row r="36" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+    </row>
+    <row r="37" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+    </row>
+    <row r="38" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+    </row>
+    <row r="39" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+    </row>
+    <row r="40" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+    </row>
+    <row r="41" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
+    </row>
+    <row r="42" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4"/>
+    </row>
+    <row r="43" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+    </row>
+    <row r="44" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+    </row>
+    <row r="45" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+    </row>
+    <row r="46" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
+    </row>
+    <row r="47" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4"/>
+    </row>
+    <row r="48" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+    </row>
+    <row r="49" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+    </row>
+    <row r="50" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+    </row>
+    <row r="51" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+    </row>
+    <row r="52" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4"/>
+    </row>
+    <row r="53" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4"/>
+    </row>
+    <row r="54" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4"/>
+    </row>
+    <row r="55" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4"/>
+    </row>
+    <row r="56" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4"/>
+    </row>
+    <row r="57" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4"/>
+    </row>
+    <row r="58" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4"/>
+    </row>
+    <row r="59" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4"/>
+    </row>
+    <row r="60" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="4"/>
+    </row>
+    <row r="61" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4"/>
+    </row>
+    <row r="62" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="4"/>
+    </row>
+    <row r="63" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4"/>
+    </row>
+    <row r="64" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="4"/>
+    </row>
+    <row r="65" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="4"/>
+    </row>
+    <row r="66" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4"/>
+    </row>
+    <row r="67" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4"/>
+    </row>
+    <row r="68" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="4"/>
+    </row>
+    <row r="69" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4"/>
+    </row>
+    <row r="70" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4"/>
+    </row>
+    <row r="71" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4"/>
+    </row>
+    <row r="72" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="4"/>
+    </row>
+    <row r="73" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4"/>
+    </row>
+    <row r="74" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4"/>
+    </row>
+    <row r="75" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4"/>
+    </row>
+    <row r="76" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="4"/>
+    </row>
+    <row r="77" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="4"/>
+    </row>
+    <row r="78" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4"/>
+    </row>
+    <row r="79" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4"/>
+    </row>
+    <row r="80" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4"/>
+    </row>
+    <row r="81" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4"/>
+    </row>
+    <row r="82" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4"/>
+    </row>
+    <row r="83" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="4"/>
+    </row>
+    <row r="84" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4"/>
+    </row>
+    <row r="85" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="4"/>
+    </row>
+    <row r="86" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4"/>
+    </row>
+    <row r="87" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4"/>
+    </row>
+    <row r="88" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4"/>
+    </row>
+    <row r="89" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4"/>
+    </row>
+    <row r="90" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4"/>
+    </row>
+    <row r="91" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="4"/>
+    </row>
+    <row r="92" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4"/>
+    </row>
+    <row r="93" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="4"/>
+    </row>
+    <row r="94" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="4"/>
+    </row>
+    <row r="95" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="4"/>
+    </row>
+    <row r="96" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4"/>
+    </row>
+    <row r="97" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="4"/>
+    </row>
+    <row r="98" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="4"/>
+    </row>
+    <row r="99" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="4"/>
+    </row>
+    <row r="100" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="4"/>
+    </row>
+    <row r="101" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010001E48B58A68BE64E9120D347E3E06B3A" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="2f90046ec77328b7f86417d2e03b3d33">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="851b35d3-0456-4d6a-bc2f-da927e91d158" xmlns:ns3="19483571-f922-4e8e-9c1c-26f0a2252132" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c815006ac2d4f05ee97fdd57e40d8e38" ns2:_="" ns3:_="">
     <xsd:import namespace="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
@@ -14929,34 +22606,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32608D25-EC36-42FE-A1DC-F778995A6799}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD3D529-BCD3-4ECD-9B2A-42924892FFCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
+    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B4D9D5-B351-46EB-A728-C3362FE437D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B4D9D5-B351-46EB-A728-C3362FE437D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD3D529-BCD3-4ECD-9B2A-42924892FFCB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32608D25-EC36-42FE-A1DC-F778995A6799}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
+    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>